--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
   </sheets>
 </workbook>
 </file>
@@ -43,15 +43,15 @@
     </border>
   </borders>
   <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>

--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -99,4 +99,14 @@
   </sheetData>
   <autoFilter ref="A1:C2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="DateProperty"/>
+    <column index="2" property="DateTimeProperty"/>
+    <column index="3" property="DateTimeOffsetProperty"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -9,10 +9,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-MM-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy-MM-dd HH:mm:ss z"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -51,7 +50,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -61,7 +61,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
   </cols>
   <sheetData>

--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -60,9 +60,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -60,9 +60,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
